--- a/artfynd/A 38429-2024 artfynd.xlsx
+++ b/artfynd/A 38429-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597632</v>
+        <v>121598018</v>
       </c>
       <c r="B3" t="n">
-        <v>97062</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,31 +807,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666630</v>
+        <v>666520</v>
       </c>
       <c r="R3" t="n">
-        <v>6558688</v>
+        <v>6558670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +897,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,17 +908,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Anneli Ahlroth, Britta Ahlgren</t>
+          <t>Ulla Sebestyen, Britta Ahlgren, Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121598018</v>
+        <v>121597632</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>97062</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,35 +927,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666520</v>
+        <v>666630</v>
       </c>
       <c r="R4" t="n">
-        <v>6558670</v>
+        <v>6558688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,6 +1013,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Britta Ahlgren, Anneli Ahlroth</t>
+          <t>Ulla Sebestyen, Anneli Ahlroth, Britta Ahlgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 38429-2024 artfynd.xlsx
+++ b/artfynd/A 38429-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121597632</v>
+        <v>121597937</v>
       </c>
       <c r="B2" t="n">
-        <v>97070</v>
+        <v>57248</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666630</v>
+        <v>666532</v>
       </c>
       <c r="R2" t="n">
-        <v>6558688</v>
+        <v>6558691</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121597937</v>
+        <v>121598018</v>
       </c>
       <c r="B3" t="n">
-        <v>57248</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,7 +833,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -840,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666532</v>
+        <v>666520</v>
       </c>
       <c r="R3" t="n">
-        <v>6558691</v>
+        <v>6558670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,17 +908,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Anneli Ahlroth, Britta Ahlgren</t>
+          <t>Ulla Sebestyen, Britta Ahlgren, Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121598018</v>
+        <v>121597632</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>97070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,35 +927,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666520</v>
+        <v>666630</v>
       </c>
       <c r="R4" t="n">
-        <v>6558670</v>
+        <v>6558688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,6 +1013,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Britta Ahlgren, Anneli Ahlroth</t>
+          <t>Ulla Sebestyen, Anneli Ahlroth, Britta Ahlgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
